--- a/rtos-api-analysis/results/tizenrt_runtime_info_walltime.xlsx
+++ b/rtos-api-analysis/results/tizenrt_runtime_info_walltime.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J146"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>212.4578</v>
+        <v>125063.2481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -499,27 +499,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.297</v>
+        <v>0.2427</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.142099999999999</v>
+        <v>22.8473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17528.1278</v>
+        <v>41198.4766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -643,27 +643,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>130053</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0092</v>
+        <v>0.0154</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.0646</v>
+        <v>13.474</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0028</v>
+        <v>0.0072</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1511</v>
+        <v>18.3468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -867,11 +867,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mq_timedreceive</t>
+          <t>get_errno</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24409.2422</v>
+        <v>0.0157</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -879,31 +879,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.8788</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -915,11 +915,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pthread_cancel</t>
+          <t>mq_timedreceive</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20896.2</v>
+        <v>47134.5352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -927,31 +927,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5249</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>341635</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20566301</t>
+          <t>1433011</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>316154</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -963,11 +963,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>setsockopt</t>
+          <t>pthread_cancel</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0111</v>
+        <v>36001.2133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -975,31 +975,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.462</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>140024</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7077827</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>123220</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1011,11 +1011,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mmap</t>
+          <t>setsockopt</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0127</v>
+        <v>0.0169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1059,11 +1059,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kill</t>
+          <t>mmap</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>322.7501</v>
+        <v>0.0335</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1071,21 +1071,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3826</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1280907</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1107,11 +1107,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pthread_cond_signal</t>
+          <t>kill</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9818</v>
+        <v>1661.5645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4367</v>
+        <v>0.3826</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>1280907</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1155,11 +1155,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>unsetenv</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.6583</v>
+        <v>0.0232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5824</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1203,11 +1203,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mq_getattr</t>
+          <t>pthread_cond_signal</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1168</v>
+        <v>12.6552</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.4367</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1251,11 +1251,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clock</t>
+          <t>unsetenv</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0046</v>
+        <v>4.7333</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1263,21 +1263,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.5824</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1299,11 +1299,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sched_getscheduler</t>
+          <t>mq_getattr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1341</v>
+        <v>0.5052</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1311,21 +1311,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6429</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1347,11 +1347,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>clock</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0026</v>
+        <v>0.0051</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1395,11 +1395,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fin_wait</t>
+          <t>sched_getscheduler</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.3733</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1407,21 +1407,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6911</v>
+        <v>0.6429</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1443,11 +1443,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pthread_mutex_destroy</t>
+          <t>close</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24.304</v>
+        <v>0.0029</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.5094</v>
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1491,11 +1491,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sigpending</t>
+          <t>fin_wait</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2456</v>
+        <v>0.0304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1503,21 +1503,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.6911</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1539,11 +1539,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>execv</t>
+          <t>pthread_mutex_destroy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0191</v>
+        <v>102.2786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1551,21 +1551,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.5094</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1587,11 +1587,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>send</t>
+          <t>sigpending</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0265</v>
+        <v>1.9034</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>477</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1635,11 +1635,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>getpid</t>
+          <t>execv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0034</v>
+        <v>0.0149</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.913</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1683,11 +1683,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pthread_setspecific</t>
+          <t>send</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0422</v>
+        <v>0.0335</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1695,21 +1695,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1731,11 +1731,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>getpid</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1779,11 +1779,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>task_restart</t>
+          <t>pthread_setspecific</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28835.6452</v>
+        <v>0.0888</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1791,31 +1791,31 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2031</v>
+        <v>0.975</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1827,11 +1827,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pipe</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0279</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1875,11 +1875,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>recvmsg</t>
+          <t>task_restart</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0153</v>
+        <v>36001.1317</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1887,31 +1887,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.1915</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41893</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2874315</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1923,11 +1923,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aio_write</t>
+          <t>pipe</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0014</v>
+        <v>0.028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1935,31 +1935,31 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1971,11 +1971,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sem_trywait</t>
+          <t>mq_notify</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9374</v>
+        <v>0.9254</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.8556</v>
+        <v>0.8993</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2019,11 +2019,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mq_setattr</t>
+          <t>recvmsg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1675</v>
+        <v>0.0193</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2035,17 +2035,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2067,11 +2067,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pread</t>
+          <t>aio_write</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0132</v>
+        <v>0.012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2079,31 +2079,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2115,11 +2115,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sendto</t>
+          <t>sem_trywait</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0182</v>
+        <v>4.7416</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2127,21 +2127,21 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.8556</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2163,11 +2163,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rename</t>
+          <t>mq_setattr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0364</v>
+        <v>0.5949</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2211,11 +2211,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>opendir</t>
+          <t>pread</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0362</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2259,11 +2259,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pthread_key_create</t>
+          <t>sendto</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2738</v>
+        <v>0.0445</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.8768</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2307,11 +2307,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>clock_settime</t>
+          <t>rename</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0785</v>
+        <v>0.0722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2319,21 +2319,21 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.9802999999999999</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2355,11 +2355,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aio_read</t>
+          <t>opendir</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0014</v>
+        <v>0.0265</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2403,11 +2403,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>boardctl</t>
+          <t>pthread_key_create</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0029</v>
+        <v>1.197</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0.8768</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2451,11 +2451,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>shmat</t>
+          <t>clock_settime</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.011</v>
+        <v>0.2934</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>299</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2499,11 +2499,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pthread_setschedprio</t>
+          <t>aio_read</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7.1423</v>
+        <v>0.0016</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2511,31 +2511,31 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.8793</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2547,11 +2547,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>waitpid</t>
+          <t>boardctl</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15462.7739</v>
+        <v>0.0068</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2559,31 +2559,31 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2951</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2595,11 +2595,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>task_setcanceltype</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.01</v>
+        <v>0.0118</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2643,11 +2643,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>closedir</t>
+          <t>poll</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0195</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2691,11 +2691,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stat</t>
+          <t>timer_settime</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0171</v>
+        <v>98451.79979999999</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2703,31 +2703,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0.1192</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2739,11 +2739,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mkdir</t>
+          <t>shmat</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0089</v>
+        <v>0.028</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2787,11 +2787,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dup2</t>
+          <t>pthread_setschedprio</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0034</v>
+        <v>43.7942</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0.8793</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>467</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>467</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2835,11 +2835,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sem_wait</t>
+          <t>waitpid</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.6257</v>
+        <v>194486.0276</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2847,31 +2847,31 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.4022</v>
+        <v>0.2951</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>837</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2883,11 +2883,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mq_open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0144</v>
+        <v>0.029</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2931,11 +2931,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>up_assert</t>
+          <t>closedir</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0139</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2979,11 +2979,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pthread_exit</t>
+          <t>fstatfs</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.1044</v>
+        <v>0.0106</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0578</v>
+        <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3027,11 +3027,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>statfs</t>
+          <t>stat</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0262</v>
+        <v>0.0704</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3075,11 +3075,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>get_environ_ptr</t>
+          <t>mkdir</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0542</v>
+        <v>0.0338</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.9506</v>
+        <v>1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3123,11 +3123,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>getsockname</t>
+          <t>dup2</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0193</v>
+        <v>0.0111</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3171,11 +3171,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>getsockopt</t>
+          <t>sem_wait</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0182</v>
+        <v>20.2017</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3183,21 +3183,21 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0.4022</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3219,11 +3219,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>connect</t>
+          <t>mq_open</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0126</v>
+        <v>0.0364</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3267,11 +3267,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>timer_create</t>
+          <t>up_assert</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6652</v>
+        <v>0.051</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3279,21 +3279,21 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.5314</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3315,11 +3315,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>pthread_sigmask</t>
+          <t>pthread_exit</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.5678</v>
+        <v>2.8377</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1259</v>
+        <v>0.0578</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3363,11 +3363,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>pgalloc</t>
+          <t>statfs</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0029</v>
+        <v>0.0682</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3411,11 +3411,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ioctl</t>
+          <t>get_environ_ptr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0032</v>
+        <v>0.1585</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0.9506</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3459,11 +3459,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sem_setprotocol</t>
+          <t>pthread_kill</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4133</v>
+        <v>887.052</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.6432</v>
+        <v>0.3876</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1507023</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3507,11 +3507,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dup</t>
+          <t>getsockname</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0053</v>
+        <v>0.0679</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3555,11 +3555,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>shutdown</t>
+          <t>getsockopt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0029</v>
+        <v>0.0149</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3603,11 +3603,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sem_unlink</t>
+          <t>connect</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0104</v>
+        <v>0.038</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3651,11 +3651,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>clock_getres</t>
+          <t>timer_create</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.037</v>
+        <v>3.3404</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.5314</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3699,11 +3699,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>exec</t>
+          <t>listen</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0015</v>
+        <v>0.0029</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3711,31 +3711,31 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3747,11 +3747,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>nanosleep</t>
+          <t>sem_post</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5418.8148</v>
+        <v>7.929</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3759,31 +3759,31 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.6529</v>
+        <v>0.4167</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>188</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3795,11 +3795,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>readdir</t>
+          <t>pthread_sigmask</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0107</v>
+        <v>9.318300000000001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0.1259</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3843,11 +3843,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>setenv</t>
+          <t>pgalloc</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.6104</v>
+        <v>0.0062</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3855,31 +3855,31 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.6336000000000001</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3891,11 +3891,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>pthread_join</t>
+          <t>ioctl</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>104.0253</v>
+        <v>0.0106</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3903,31 +3903,31 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.5315</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>567105</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3939,11 +3939,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sched_lock</t>
+          <t>sem_setprotocol</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0105</v>
+        <v>0.9918</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.7632</v>
+        <v>0.6432</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>723</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3987,11 +3987,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>task_setcancelstate</t>
+          <t>dup</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.3249</v>
+        <v>0.0026</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.0361</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4035,11 +4035,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>task_testcancel</t>
+          <t>shutdown</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0019</v>
+        <v>0.0151</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4083,11 +4083,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>putenv</t>
+          <t>sem_unlink</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>58.6708</v>
+        <v>0.0588</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4095,31 +4095,31 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.6745</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4131,11 +4131,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>shmget</t>
+          <t>sched_lockcount</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4179,11 +4179,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sem_open</t>
+          <t>clock_getres</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0106</v>
+        <v>0.0446</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4191,21 +4191,21 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4227,11 +4227,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pthread_detach</t>
+          <t>exec</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>108.4234</v>
+        <v>0.0023</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4239,31 +4239,31 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.4021</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>531402</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4275,11 +4275,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sem_destroy</t>
+          <t>nanosleep</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.3804</v>
+        <v>57725.5269</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4287,31 +4287,31 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.6178</v>
+        <v>0.6529</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>75058</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>815</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4323,11 +4323,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>seekdir</t>
+          <t>readdir</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0149</v>
+        <v>0.045</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4371,11 +4371,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>clock_gettime</t>
+          <t>setenv</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.098</v>
+        <v>20.239</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4383,31 +4383,31 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4419,11 +4419,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pthread_cond_wait</t>
+          <t>pthread_join</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0998</v>
+        <v>262.9332</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4431,31 +4431,31 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.0673</v>
+        <v>0.5315</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>567105</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4467,11 +4467,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>pthread_create</t>
+          <t>sched_lock</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7359.8025</v>
+        <v>0.0213</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4479,31 +4479,31 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.169</v>
+        <v>0.7632</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4515,11 +4515,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>fsync</t>
+          <t>task_setcancelstate</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0025</v>
+        <v>1.1696</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0.0361</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4563,11 +4563,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>timer_gettime</t>
+          <t>task_testcancel</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5236</v>
+        <v>0.002</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.9286</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4611,11 +4611,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>pthread_mutex_lock</t>
+          <t>putenv</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.467</v>
+        <v>184.7154</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4623,31 +4623,31 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.4952</v>
+        <v>0.6745</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>191008</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fs_ioctl</t>
+          <t>shmget</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4707,11 +4707,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>pwrite</t>
+          <t>mq_close</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0116</v>
+        <v>0.0128</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4755,11 +4755,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>atexit</t>
+          <t>sem_open</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0013</v>
+        <v>0.0507</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4767,31 +4767,31 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4803,11 +4803,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>clearenv</t>
+          <t>pthread_tryjoin_np</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.0936</v>
+        <v>199.8258</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4815,31 +4815,31 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.9581</v>
+        <v>0.4093</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>679402</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4851,11 +4851,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ftruncate</t>
+          <t>pthread_detach</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0029</v>
+        <v>385.5985</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4863,31 +4863,31 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0.4021</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>531402</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4899,11 +4899,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>_exit</t>
+          <t>sem_destroy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0024</v>
+        <v>2.5579</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4911,31 +4911,31 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0.6178</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4947,11 +4947,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mq_receive</t>
+          <t>seekdir</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>21.475</v>
+        <v>0.0325</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4959,31 +4959,31 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>116587</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4995,11 +4995,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pthread_setschedparam</t>
+          <t>clock_gettime</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7.0978</v>
+        <v>0.2288</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5007,21 +5007,21 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.8961</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>344</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5043,11 +5043,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>pthread_cond_wait</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0109</v>
+        <v>0.526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5055,21 +5055,21 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0.0673</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5091,11 +5091,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>task_delete</t>
+          <t>pthread_create</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7574.6329</v>
+        <v>17972.6217</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5103,31 +5103,31 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.469</v>
+        <v>0.169</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>146461</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>7895101</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>130564</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5139,11 +5139,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sem_timedwait</t>
+          <t>fsync</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>24181.1039</v>
+        <v>0.0025</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5151,31 +5151,31 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.4145</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5187,11 +5187,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>timer_getoverrun</t>
+          <t>timer_gettime</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0162</v>
+        <v>3.5969</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5199,21 +5199,21 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.9111</v>
+        <v>0.9286</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5235,11 +5235,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sched_getparam</t>
+          <t>pthread_mutex_lock</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.2892</v>
+        <v>105.3179</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5247,21 +5247,21 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8625</v>
+        <v>0.4952</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>191008</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5283,11 +5283,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rewinddir</t>
+          <t>task_create</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0138</v>
+        <v>17535.1875</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5295,31 +5295,31 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0.188</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7816619</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>171021</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5331,11 +5331,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>pthread_cond_broadcast</t>
+          <t>fs_ioctl</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.9361</v>
+        <v>0.0187</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.4363</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5379,11 +5379,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>pthread_mutex_consistent</t>
+          <t>pwrite</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>8.8367</v>
+        <v>0.0105</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.4796</v>
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5427,11 +5427,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sched_setparam</t>
+          <t>atexit</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.3291</v>
+        <v>0.0013</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5439,31 +5439,31 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.8829</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5475,11 +5475,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>gettimeofday</t>
+          <t>clearenv</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0793</v>
+        <v>65.76179999999999</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5487,31 +5487,31 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.8333</v>
+        <v>0.9581</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>326</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5523,11 +5523,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mount</t>
+          <t>ftruncate</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0259</v>
+        <v>0.0104</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5571,11 +5571,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>_exit</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>17701.8707</v>
+        <v>0.0023</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5583,31 +5583,31 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2739</v>
+        <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5619,11 +5619,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sigaction</t>
+          <t>mq_receive</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.3748</v>
+        <v>47.5561</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5631,31 +5631,31 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.7847</v>
+        <v>0.955</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5667,11 +5667,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>shmctl</t>
+          <t>pthread_setschedparam</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0129</v>
+        <v>41.8057</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5679,21 +5679,21 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0.8961</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>439</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5715,11 +5715,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mq_send</t>
+          <t>write</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1232.1133</v>
+        <v>0.0199</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5727,21 +5727,21 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.4902</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>4991852</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5763,11 +5763,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sched_unlock</t>
+          <t>task_delete</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0135</v>
+        <v>32442.3308</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5775,31 +5775,31 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.7789</v>
+        <v>0.469</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>146461</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>7895101</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>121</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5811,11 +5811,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>umount</t>
+          <t>sem_timedwait</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0101</v>
+        <v>46665.5573</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5823,31 +5823,31 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0.4145</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28445</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5859,11 +5859,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>aio_cancel</t>
+          <t>timer_getoverrun</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0013</v>
+        <v>0.0785</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5871,31 +5871,31 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.9111</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5907,11 +5907,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>recv</t>
+          <t>sched_getparam</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0106</v>
+        <v>1.2781</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5919,21 +5919,21 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0.8625</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>571</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5955,11 +5955,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mq_unlink</t>
+          <t>rewinddir</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0128</v>
+        <v>0.0098</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6003,11 +6003,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>prctl</t>
+          <t>pthread_cond_broadcast</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.8858</v>
+        <v>19.5079</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.8884</v>
+        <v>0.4363</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6051,11 +6051,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sigprocmask</t>
+          <t>pthread_mutex_consistent</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2.5567</v>
+        <v>25.7709</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -6063,21 +6063,21 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.1182</v>
+        <v>0.4796</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>601</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6099,11 +6099,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>pthread_mutex_init</t>
+          <t>sched_setparam</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.9849</v>
+        <v>29.4519</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6111,21 +6111,21 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8829</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6147,11 +6147,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>bind</t>
+          <t>gettimeofday</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.01</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6159,21 +6159,21 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6195,11 +6195,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>fs_fdopen</t>
+          <t>mount</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0097</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -6243,11 +6243,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sigwaitinfo</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2309.7437</v>
+        <v>39508.3236</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6255,31 +6255,31 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.669</v>
+        <v>0.2739</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>84148</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>841</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6291,11 +6291,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>pthread_cond_timedwait</t>
+          <t>sigaction</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>7.7684</v>
+        <v>68.12520000000001</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6303,31 +6303,31 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.2094</v>
+        <v>0.7847</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>699</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -6339,11 +6339,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>on_exit</t>
+          <t>shmctl</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.0019</v>
+        <v>0.0388</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6387,11 +6387,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>pthread_key_delete</t>
+          <t>mq_send</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>5.9444</v>
+        <v>5001.7348</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6399,21 +6399,21 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.898</v>
+        <v>0.4902</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79827</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4991852</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79827</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6435,11 +6435,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>getpeername</t>
+          <t>sched_unlock</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0241</v>
+        <v>0.0455</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6447,21 +6447,21 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0.7789</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6483,11 +6483,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>unlink</t>
+          <t>fcntl</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0128</v>
+        <v>0.0027</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6531,11 +6531,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>aio_fsync</t>
+          <t>umount</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0016</v>
+        <v>0.0164</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6543,31 +6543,31 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6579,11 +6579,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>set_errno</t>
+          <t>aio_cancel</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.027</v>
+        <v>0.0141</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6591,31 +6591,31 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6627,11 +6627,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>pthread_getschedparam</t>
+          <t>mkfifo</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.422</v>
+        <v>0.0107</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6639,21 +6639,21 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.791</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6675,11 +6675,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sigtimedwait</t>
+          <t>recv</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>13548.2227</v>
+        <v>0.0146</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6687,31 +6687,31 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.669</v>
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6723,11 +6723,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>select</t>
+          <t>mq_unlink</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0386</v>
+        <v>0.0524</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -6771,11 +6771,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>vfork</t>
+          <t>prctl</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0021</v>
+        <v>2.0791</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6783,21 +6783,21 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0.8884</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>617</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6819,11 +6819,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sem_close</t>
+          <t>sigprocmask</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.01</v>
+        <v>9.4719</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0.1182</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6867,11 +6867,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sched_yield</t>
+          <t>pthread_mutex_init</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0092</v>
+        <v>10.6831</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6879,21 +6879,21 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.2027</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6915,11 +6915,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>recvfrom</t>
+          <t>bind</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0312</v>
+        <v>0.0108</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6963,11 +6963,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sigsuspend</t>
+          <t>fs_fdopen</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6867</v>
+        <v>0.029</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.1088</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7011,11 +7011,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>pthread_getspecific</t>
+          <t>sigwaitinfo</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0469</v>
+        <v>133936.5725</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7023,31 +7023,31 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.9718</v>
+        <v>0.669</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>51975</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7059,11 +7059,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sigqueue</t>
+          <t>pthread_cond_timedwait</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>337.8438</v>
+        <v>44.8925</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7071,31 +7071,31 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.411</v>
+        <v>0.2094</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1302519</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7107,11 +7107,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sched_getstreams</t>
+          <t>on_exit</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.0036</v>
+        <v>0.0426</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.7097</v>
+        <v>1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7155,11 +7155,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>pthread_key_delete</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1581.9901</v>
+        <v>15.5361</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7167,31 +7167,31 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.3883</v>
+        <v>0.898</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>195724</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7203,11 +7203,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>fstat</t>
+          <t>getpeername</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0098</v>
+        <v>0.0321</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -7251,11 +7251,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>lseek</t>
+          <t>unlink</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0035</v>
+        <v>0.0095</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -7299,11 +7299,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>timer_delete</t>
+          <t>aio_fsync</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>19.3891</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7311,31 +7311,31 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.9779</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7347,11 +7347,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sched_rr_get_interval</t>
+          <t>set_errno</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.1877</v>
+        <v>0.0121</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7359,21 +7359,21 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.8759</v>
+        <v>0.9</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7395,44 +7395,860 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>pthread_getschedparam</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1.8388</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>sigtimedwait</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>37008.7627</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>49776</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>vfork</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>sem_close</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>sched_yield</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>recvfrom</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>sigsuspend</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2.6006</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>pthread_getspecific</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>sigqueue</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1679.2575</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>21151</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1302519</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>21151</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>sched_getstreams</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>4589.1932</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>8631</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>195724</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2341</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fstat</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>lseek</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>timer_delete</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>83.0326</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>90862</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>sched_rr_get_interval</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>rmdir</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>run.stats</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>Total Finished</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B163" t="n">
         <v>1</v>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr">
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
